--- a/演示知识库资料/03-模拟企业资料/产品套餐与服务时效.xlsx
+++ b/演示知识库资料/03-模拟企业资料/产品套餐与服务时效.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="套餐价格" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'资料说明'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'资料说明'!$A$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'套餐价格'!$A$1:$C$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -450,11 +450,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -546,25 +546,56 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>全文说明</t>
+          <t>正文第 1 部分</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>资料摘要：产品套餐与服务时效的演示检索资料（PLAN-SLA-2026）。
-一、资料用途与阅读边界。产品套餐与服务时效的文档代号是 PLAN-SLA-2026，它是一份专为演示知识库准备的虚构中文资料。资料面向学习者、演示人员和维护人员，目的不是替代真实业务制度，而是让提问者能够根据原文核对术语、数字、日期和状态。回答前应先识别问题的范围，再从本文件或明确关联的文件中检索证据；资料没有写出的结论必须说明知识库缺少答案，不能靠常识补写。内容不含真实账号、密钥、客户信息或公司机密，后续生成时应保持 UTF-8 中文可读、标题清晰，并保留文件名以便验证引用来源。
-二、核心规则与可核对事实。Basic 为 ¥99/月且响应 8 小时；Pro 为 ¥399/月且响应 2 小时；Enterprise 为定制且响应 30 分钟；续费提前 15 天通知。这些事实需要作为完整流程理解：执行前检查前提，执行中记录状态，执行后根据结果决定下一步。数字问题必须带上单位和条件，日期问题必须带上对应事项，状态问题必须区分可继续处理和需要排查两种结果。引用本资料时，应同时给出文件名与能定位规则的摘录，不能只留下脱离语境的短句。演示人员可以先针对一个精确事实提问，再把本文件与关联文件组合提问，以观察检索、重排序和回答是否保持一致。
-三、执行提示与关联资料。退款审核和退款时限以《客服退款FAQ.md》为准，套餐响应时间不能替代退款规则。。当发现服务未就绪、资料处理失败或规则冲突时，应保留错误原因并按排查路径处理，而不是猜测成功结果。每次演示都应把测试问题与知识资料分开保存，测试问题及预期答案不得上传到知识库，避免答案文本反向污染检索。此段同时提醒使用者：示例中的名称、价格、日期和时限仅为教学用虚构数据；若问题超出本资料范围，正确的通过标准是明确承认缺少依据，并请提问者补充可检索的材料。为便于复盘，每次问答还应记录问题、命中的资料代号、引用摘录和未覆盖的边界，作为下一轮资料改进的依据。记录应采用清晰、可复现的中文描述，避免把推测写成事实；需要多人协作时，应标明负责角色、处理时间和复核结果。</t>
+          <t>一、资料用途与阅读边界。产品套餐与服务时效的文档代号是 PLAN-SLA-2026，它是一份专为演示知识库准备的虚构中文资料。资料面向学习者、演示人员和维护人员，目的不是替代真实业务制度，而是让提问者能够根据原文核对术语、数字、日期和状态。回答前应先识别问题的范围，再从本文件或明确关联的文件中检索证据；资料没有写出的结论必须说明知识库缺少答案，不能靠常识补写。内容不含真实账号、密钥、客户信息或公司机密，后续生成时应保持 UTF-8 中文可读、标题清晰，并保留文件名以便验证引用来源。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>用于确保表格文件具备等价的信息密度</t>
+          <t>保留完整正文，供知识库按段检索</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>正文第 2 部分</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>二、核心规则与可核对事实。Basic 为 ¥99/月且响应 8 小时；Pro 为 ¥399/月且响应 2 小时；Enterprise 为定制且响应 30 分钟；续费提前 15 天通知。这些事实需要作为完整流程理解：执行前检查前提，执行中记录状态，执行后根据结果决定下一步。数字问题必须带上单位和条件，日期问题必须带上对应事项，状态问题必须区分可继续处理和需要排查两种结果。引用本资料时，应同时给出文件名与能定位规则的摘录，不能只留下脱离语境的短句。演示人员可以先针对一个精确事实提问，再把本文件与关联文件组合提问，以观察检索、重排序和回答是否保持一致。</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>保留完整正文，供知识库按段检索</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>正文第 3 部分</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>三、执行提示与关联资料。退款审核和退款时限以《客服退款FAQ.md》为准，套餐响应时间不能替代退款规则。当发现服务未就绪、资料处理失败或规则冲突时，应保留错误原因并按排查路径处理，而不是猜测成功结果。每次演示都应把测试问题与知识资料分开保存，测试问题及预期答案不得上传到知识库，避免答案文本反向污染检索。此段同时提醒使用者：示例中的名称、价格、日期和时限仅为教学用虚构数据；若问题超出本资料范围，正确的通过标准是明确承认缺少依据，并请提问者补充可检索的材料。为便于复盘，每次问答还应记录问题、命中的资料代号、引用摘录和未覆盖的边界，作为下一轮资料改进的依据。记录应采用清晰、可复现的中文描述，避免把推测写成事实；需要多人协作时，应标明负责角色、处理时间和复核结果。</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>保留完整正文，供知识库按段检索</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C6"/>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -578,8 +609,8 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -749,7 +780,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>三、执行提示与关联资料。退款审核和退款时限以《客服退款FAQ.md》为准，套餐响应时间不能替代退款规则。。当发现服务未就绪、资料处理失败或规则冲突时，应保留错误原因并按排查路径处理，而不是猜测成功结果。每次演示都应把测试问题与知识资料分开保存，测试问题及预期答</t>
+          <t>三、执行提示与关联资料。退款审核和退款时限以《客服退款FAQ.md》为准，套餐响应时间不能替代退款规则。当发现服务未就绪、资料处理失败或规则冲突时，应保留错误原因并按排查路径处理，而不是猜测成功结果。每次演示都应把测试问题与知识资料分开保存，测试问题及预期答案</t>
         </is>
       </c>
     </row>
@@ -766,7 +797,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>按排查路径处理，而不是猜测成功结果。每次演示都应把测试问题与知识资料分开保存，测试问题及预期答案不得上传到知识库，避免答案文本反向污染检索。此段同时提醒使用者：示例中的名称、价格、日期和时限仅为教学用虚构数据；若问题超出本资料范围，正确的通过标准是明确承认缺少</t>
+          <t>排查路径处理，而不是猜测成功结果。每次演示都应把测试问题与知识资料分开保存，测试问题及预期答案不得上传到知识库，避免答案文本反向污染检索。此段同时提醒使用者：示例中的名称、价格、日期和时限仅为教学用虚构数据；若问题超出本资料范围，正确的通过标准是明确承认缺少依</t>
         </is>
       </c>
     </row>
@@ -783,7 +814,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>的名称、价格、日期和时限仅为教学用虚构数据；若问题超出本资料范围，正确的通过标准是明确承认缺少依据，并请提问者补充可检索的材料。为便于复盘，每次问答还应记录问题、命中的资料代号、引用摘录和未覆盖的边界，作为下一轮资料改进的依据。记录应采用清晰、可复现的中文描述</t>
+          <t>名称、价格、日期和时限仅为教学用虚构数据；若问题超出本资料范围，正确的通过标准是明确承认缺少依据，并请提问者补充可检索的材料。为便于复盘，每次问答还应记录问题、命中的资料代号、引用摘录和未覆盖的边界，作为下一轮资料改进的依据。记录应采用清晰、可复现的中文描述，</t>
         </is>
       </c>
     </row>
@@ -800,7 +831,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>的资料代号、引用摘录和未覆盖的边界，作为下一轮资料改进的依据。记录应采用清晰、可复现的中文描述，避免把推测写成事实；需要多人协作时，应标明负责角色、处理时间和复核结果。</t>
+          <t>资料代号、引用摘录和未覆盖的边界，作为下一轮资料改进的依据。记录应采用清晰、可复现的中文描述，避免把推测写成事实；需要多人协作时，应标明负责角色、处理时间和复核结果。</t>
         </is>
       </c>
     </row>
